--- a/output/pdf_financials_xlsx/AUQ.xlsx
+++ b/output/pdf_financials_xlsx/AUQ.xlsx
@@ -6201,28 +6201,28 @@
         <v>2.393875</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.393875</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.393875</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.484869</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.514468</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.515968</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.515968</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>2.526468</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>2.682097</v>
       </c>
     </row>
     <row r="93">
@@ -7725,7 +7725,7 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.013885</v>
+        <v>-0.839062</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>1.542378</v>
@@ -7749,28 +7749,28 @@
         <v>0</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.035</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.274</v>
+        <v>0.21476</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.212294</v>
+        <v>0.112294</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.362914</v>
+        <v>0.180753</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.016007</v>
+        <v>-0.009213000000000001</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0.884975</v>
+        <v>0.612408</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>0.5743740000000001</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0.533602</v>
+        <v>0.436051</v>
       </c>
     </row>
     <row r="119">
@@ -10340,7 +10340,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -11182,7 +11186,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -12448,7 +12456,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -13182,7 +13194,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -14342,7 +14358,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -14870,7 +14890,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -15930,7 +15954,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -23260,7 +23288,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -27450,7 +27482,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -34514,7 +34550,11 @@
           <t>Deferred exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AUQ.xlsx
+++ b/output/pdf_financials_xlsx/AUQ.xlsx
@@ -961,34 +961,34 @@
         <v>0.134807</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.217758</v>
+        <v>2.461242</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.06202</v>
+        <v>0.11852</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.122728</v>
+        <v>0.140978</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.322883</v>
+        <v>0.349473</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.274092</v>
+        <v>0.297892</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.118573</v>
+        <v>0.433662</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.111748</v>
+        <v>0.152755</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.08416999999999999</v>
+        <v>1.006809</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.07757699999999999</v>
+        <v>0.702232</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.188657</v>
+        <v>0.710943</v>
       </c>
     </row>
     <row r="11">
@@ -1022,34 +1022,34 @@
         <v>-0.134807</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.217758</v>
+        <v>-2.461242</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.06202</v>
+        <v>-0.11852</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.122728</v>
+        <v>-0.140978</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.322883</v>
+        <v>-0.349473</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.274092</v>
+        <v>-0.297892</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.118573</v>
+        <v>-0.433662</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.111748</v>
+        <v>-0.152755</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.08416999999999999</v>
+        <v>-1.006809</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.07757699999999999</v>
+        <v>-0.702232</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.188657</v>
+        <v>-0.710943</v>
       </c>
     </row>
     <row r="12">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007618</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.95711</v>
+        <v>-0.949492</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-2.679507</v>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.95711</v>
+        <v>-0.949492</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-2.679507</v>
@@ -2499,58 +2499,58 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.126222</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.120056</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.019693</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.287156</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.169882</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.142976</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.00046</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000308</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.008503</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.109423</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.166007</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.000139</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.330152</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.015018</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.134405</v>
       </c>
     </row>
     <row r="35">
@@ -2621,58 +2621,58 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.126222</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.120056</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.019693</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.287156</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.169882</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.142976</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.00046</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.000308</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.008503</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.109423</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.166007</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.000139</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.330152</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.015018</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.134405</v>
       </c>
     </row>
     <row r="37">
@@ -3353,49 +3353,49 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.175813</v>
+        <v>0.049591</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.149316</v>
+        <v>0.02926</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.039</v>
+        <v>0.019307</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.313009</v>
+        <v>0.025853</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.393785</v>
+        <v>0.223903</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.155918</v>
+        <v>0.012942</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.01469</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.006346</v>
+        <v>0.006341</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.00046</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.000308</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.008503</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.109423</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.471007</v>
+        <v>0.305</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.000139</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.330152</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0</v>
@@ -3404,7 +3404,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.172658</v>
+        <v>0.038253</v>
       </c>
     </row>
     <row r="49">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -21234,7 +21234,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
@@ -42114,7 +42114,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -42306,7 +42306,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -44072,7 +44072,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -45080,7 +45080,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -45916,7 +45916,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -54170,7 +54170,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E435" s="5" t="n">

--- a/output/pdf_financials_xlsx/AUQ.xlsx
+++ b/output/pdf_financials_xlsx/AUQ.xlsx
@@ -766,10 +766,10 @@
         <v>0.211552</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.210651</v>
+        <v>0.220651</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.137585</v>
+        <v>0.178585</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.075664</v>
@@ -949,10 +949,10 @@
         <v>0.251244</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.273286</v>
+        <v>0.283286</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.140849</v>
+        <v>0.181849</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.081664</v>
@@ -1010,10 +1010,10 @@
         <v>-1.942542</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.273286</v>
+        <v>-0.283286</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.140849</v>
+        <v>-0.181849</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>-0.081664</v>
@@ -1370,7 +1370,7 @@
         <v>2.679507</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.031427</v>
+        <v>-0.19157</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -2340,7 +2340,7 @@
         <v>-100</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-4.804293855787105</v>
+        <v>-29.28560072399961</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -6682,28 +6682,28 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.012109</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.009532000000000001</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006737</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.027843</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.010488</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.01558</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000584</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002815</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>-0.001424</v>
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.010505</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -28744,7 +28744,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E191" s="5" t="n">
         <v>-0.012109</v>
       </c>
@@ -31608,7 +31612,11 @@
           <t>HST/GST receivable</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -36670,7 +36678,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E267" s="5" t="n">
         <v>-0.49675</v>
       </c>
@@ -36774,7 +36786,11 @@
           <t>HST/GST recoverable</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -39814,7 +39830,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E297" s="5" t="n">
         <v>0.010505</v>
       </c>
@@ -50188,7 +50208,11 @@
           <t>Director fees (note 10)</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -50910,7 +50934,11 @@
           <t>Director fees (note 11)</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -53426,7 +53454,11 @@
           <t>Future income tax recovery (note 13)</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -54490,7 +54522,11 @@
           <t>Future income tax recovery (note 13)</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E438" s="5" t="n">
         <v>0.49675</v>
       </c>
